--- a/dataset_t6_grouped/results2/G2/G2_T1656_W0034F0001T0006Z000C1N31_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G2/G2_T1656_W0034F0001T0006Z000C1N31_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>86.7639927938115</v>
+        <v>14.09914882899437</v>
       </c>
       <c r="D2" t="n">
-        <v>81.65263554364778</v>
+        <v>13.26855327584276</v>
       </c>
       <c r="E2" t="n">
-        <v>18.70842289727105</v>
+        <v>3.040118720806546</v>
       </c>
       <c r="F2" t="n">
-        <v>16.4946284893427</v>
+        <v>2.680377129518189</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>55.05566796427118</v>
+        <v>8.946546044194067</v>
       </c>
       <c r="D3" t="n">
-        <v>51.05964376615679</v>
+        <v>8.297192112000479</v>
       </c>
       <c r="E3" t="n">
-        <v>18.70842289727105</v>
+        <v>3.040118720806546</v>
       </c>
       <c r="F3" t="n">
-        <v>16.4946284893427</v>
+        <v>2.680377129518189</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>57.9961808898659</v>
+        <v>9.424379394603211</v>
       </c>
       <c r="D4" t="n">
-        <v>53.16054460015499</v>
+        <v>8.638588497525186</v>
       </c>
       <c r="E4" t="n">
-        <v>18.70842289727105</v>
+        <v>3.040118720806546</v>
       </c>
       <c r="F4" t="n">
-        <v>16.4946284893427</v>
+        <v>2.680377129518189</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>60.24483664894428</v>
+        <v>9.789785955453446</v>
       </c>
       <c r="D5" t="n">
-        <v>58.4749549428007</v>
+        <v>9.502180178205114</v>
       </c>
       <c r="E5" t="n">
-        <v>18.70842289727105</v>
+        <v>3.040118720806546</v>
       </c>
       <c r="F5" t="n">
-        <v>16.4946284893427</v>
+        <v>2.680377129518189</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>35.61278296636616</v>
+        <v>5.787077232034502</v>
       </c>
       <c r="D6" t="n">
-        <v>31.75870318946242</v>
+        <v>5.160789268287644</v>
       </c>
       <c r="E6" t="n">
-        <v>18.70842289727105</v>
+        <v>3.040118720806546</v>
       </c>
       <c r="F6" t="n">
-        <v>16.4946284893427</v>
+        <v>2.680377129518189</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>42.18867232291193</v>
+        <v>6.855659252473188</v>
       </c>
       <c r="D7" t="n">
-        <v>43.21240358977018</v>
+        <v>7.022015583337653</v>
       </c>
       <c r="E7" t="n">
-        <v>18.70842289727105</v>
+        <v>3.040118720806546</v>
       </c>
       <c r="F7" t="n">
-        <v>16.4946284893427</v>
+        <v>2.680377129518189</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>28.90648290615764</v>
+        <v>4.697303472250617</v>
       </c>
       <c r="D8" t="n">
-        <v>30.55648540742822</v>
+        <v>4.965428878707086</v>
       </c>
       <c r="E8" t="n">
-        <v>18.70842289727105</v>
+        <v>3.040118720806546</v>
       </c>
       <c r="F8" t="n">
-        <v>16.4946284893427</v>
+        <v>2.680377129518189</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>26.00308749322484</v>
+        <v>4.225501717649037</v>
       </c>
       <c r="D9" t="n">
-        <v>27.15650016478697</v>
+        <v>4.412931276777883</v>
       </c>
       <c r="E9" t="n">
-        <v>18.70842289727105</v>
+        <v>3.040118720806546</v>
       </c>
       <c r="F9" t="n">
-        <v>16.4946284893427</v>
+        <v>2.680377129518189</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>29.33143930739819</v>
+        <v>4.766358887452205</v>
       </c>
       <c r="D10" t="n">
-        <v>30.62146788778275</v>
+        <v>4.975988531764696</v>
       </c>
       <c r="E10" t="n">
-        <v>18.70842289727105</v>
+        <v>3.040118720806546</v>
       </c>
       <c r="F10" t="n">
-        <v>16.4946284893427</v>
+        <v>2.680377129518189</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>15.49927519889078</v>
+        <v>2.518632219819752</v>
       </c>
       <c r="D11" t="n">
-        <v>11.70814013380807</v>
+        <v>1.902572771743811</v>
       </c>
       <c r="E11" t="n">
-        <v>18.70842289727105</v>
+        <v>3.040118720806546</v>
       </c>
       <c r="F11" t="n">
-        <v>16.4946284893427</v>
+        <v>2.680377129518189</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>35.34228710632451</v>
+        <v>5.743121654777734</v>
       </c>
       <c r="D12" t="n">
-        <v>38.85455910598196</v>
+        <v>6.313865854722068</v>
       </c>
       <c r="E12" t="n">
-        <v>18.70842289727105</v>
+        <v>3.040118720806546</v>
       </c>
       <c r="F12" t="n">
-        <v>16.4946284893427</v>
+        <v>2.680377129518189</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>5.340431437636405</v>
+        <v>0.8678201086159159</v>
       </c>
       <c r="D13" t="n">
-        <v>10.23189498657733</v>
+        <v>1.662682935318816</v>
       </c>
       <c r="E13" t="n">
-        <v>18.70842289727105</v>
+        <v>3.040118720806546</v>
       </c>
       <c r="F13" t="n">
-        <v>16.4946284893427</v>
+        <v>2.680377129518189</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>13.64995114232541</v>
+        <v>2.218117060627879</v>
       </c>
       <c r="D14" t="n">
-        <v>18.04356822653044</v>
+        <v>2.932079836811196</v>
       </c>
       <c r="E14" t="n">
-        <v>18.70842289727105</v>
+        <v>3.040118720806546</v>
       </c>
       <c r="F14" t="n">
-        <v>16.4946284893427</v>
+        <v>2.680377129518189</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>24.18259589008072</v>
+        <v>3.929671832138117</v>
       </c>
       <c r="D15" t="n">
-        <v>25.06209445043718</v>
+        <v>4.072590348196041</v>
       </c>
       <c r="E15" t="n">
-        <v>18.70842289727105</v>
+        <v>3.040118720806546</v>
       </c>
       <c r="F15" t="n">
-        <v>16.4946284893427</v>
+        <v>2.680377129518189</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -928,16 +928,16 @@
         <v>15</v>
       </c>
       <c r="C16" t="n">
-        <v>39.87607491959056</v>
+        <v>6.479862174433466</v>
       </c>
       <c r="D16" t="n">
-        <v>44.66591108730633</v>
+        <v>7.25821055168728</v>
       </c>
       <c r="E16" t="n">
-        <v>18.70842289727105</v>
+        <v>3.040118720806546</v>
       </c>
       <c r="F16" t="n">
-        <v>16.4946284893427</v>
+        <v>2.680377129518189</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -960,16 +960,16 @@
         <v>16</v>
       </c>
       <c r="C17" t="n">
-        <v>24.23676332656075</v>
+        <v>3.938474040566122</v>
       </c>
       <c r="D17" t="n">
-        <v>24.50176727028494</v>
+        <v>3.981537181421304</v>
       </c>
       <c r="E17" t="n">
-        <v>18.70842289727105</v>
+        <v>3.040118720806546</v>
       </c>
       <c r="F17" t="n">
-        <v>16.4946284893427</v>
+        <v>2.680377129518189</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -992,16 +992,16 @@
         <v>17</v>
       </c>
       <c r="C18" t="n">
-        <v>21.63126769457778</v>
+        <v>3.51508100036889</v>
       </c>
       <c r="D18" t="n">
-        <v>34.51371918806843</v>
+        <v>5.60847936806112</v>
       </c>
       <c r="E18" t="n">
-        <v>18.70842289727105</v>
+        <v>3.040118720806546</v>
       </c>
       <c r="F18" t="n">
-        <v>16.4946284893427</v>
+        <v>2.680377129518189</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1024,16 +1024,16 @@
         <v>18</v>
       </c>
       <c r="C19" t="n">
-        <v>51.62412076219326</v>
+        <v>8.388919623856406</v>
       </c>
       <c r="D19" t="n">
-        <v>56.71262556295947</v>
+        <v>9.215801653980913</v>
       </c>
       <c r="E19" t="n">
-        <v>18.70842289727105</v>
+        <v>3.040118720806546</v>
       </c>
       <c r="F19" t="n">
-        <v>16.4946284893427</v>
+        <v>2.680377129518189</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1056,16 +1056,16 @@
         <v>19</v>
       </c>
       <c r="C20" t="n">
-        <v>15.21422438396425</v>
+        <v>2.472311462394191</v>
       </c>
       <c r="D20" t="n">
-        <v>38.24415789337836</v>
+        <v>6.214675657673984</v>
       </c>
       <c r="E20" t="n">
-        <v>18.70842289727105</v>
+        <v>3.040118720806546</v>
       </c>
       <c r="F20" t="n">
-        <v>16.4946284893427</v>
+        <v>2.680377129518189</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1088,16 +1088,16 @@
         <v>20</v>
       </c>
       <c r="C21" t="n">
-        <v>56.94252554777224</v>
+        <v>9.253160401512989</v>
       </c>
       <c r="D21" t="n">
-        <v>64.61021824007328</v>
+        <v>10.49916046401191</v>
       </c>
       <c r="E21" t="n">
-        <v>18.70842289727105</v>
+        <v>3.040118720806546</v>
       </c>
       <c r="F21" t="n">
-        <v>16.4946284893427</v>
+        <v>2.680377129518189</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -1120,16 +1120,16 @@
         <v>21</v>
       </c>
       <c r="C22" t="n">
-        <v>37.92373463610954</v>
+        <v>6.162606878367801</v>
       </c>
       <c r="D22" t="n">
-        <v>57.86144325932111</v>
+        <v>9.402484529639681</v>
       </c>
       <c r="E22" t="n">
-        <v>18.70842289727105</v>
+        <v>3.040118720806546</v>
       </c>
       <c r="F22" t="n">
-        <v>16.4946284893427</v>
+        <v>2.680377129518189</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -1152,16 +1152,16 @@
         <v>22</v>
       </c>
       <c r="C23" t="n">
-        <v>5.499013886725558</v>
+        <v>0.8935897565929032</v>
       </c>
       <c r="D23" t="n">
-        <v>50.47253749625462</v>
+        <v>8.201787343141376</v>
       </c>
       <c r="E23" t="n">
-        <v>18.70842289727105</v>
+        <v>3.040118720806546</v>
       </c>
       <c r="F23" t="n">
-        <v>16.4946284893427</v>
+        <v>2.680377129518189</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -1184,16 +1184,16 @@
         <v>23</v>
       </c>
       <c r="C24" t="n">
-        <v>15.08984269881988</v>
+        <v>2.452099438558231</v>
       </c>
       <c r="D24" t="n">
-        <v>51.51475374994226</v>
+        <v>8.371147484365617</v>
       </c>
       <c r="E24" t="n">
-        <v>18.70842289727105</v>
+        <v>3.040118720806546</v>
       </c>
       <c r="F24" t="n">
-        <v>16.4946284893427</v>
+        <v>2.680377129518189</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
@@ -1216,16 +1216,16 @@
         <v>24</v>
       </c>
       <c r="C25" t="n">
-        <v>41.85780217871</v>
+        <v>6.801892854040376</v>
       </c>
       <c r="D25" t="n">
-        <v>40.55736694870794</v>
+        <v>6.59057212916504</v>
       </c>
       <c r="E25" t="n">
-        <v>18.70842289727105</v>
+        <v>3.040118720806546</v>
       </c>
       <c r="F25" t="n">
-        <v>16.4946284893427</v>
+        <v>2.680377129518189</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
@@ -1248,16 +1248,16 @@
         <v>25</v>
       </c>
       <c r="C26" t="n">
-        <v>40.45889596617155</v>
+        <v>6.574570594502877</v>
       </c>
       <c r="D26" t="n">
-        <v>48.11746633869149</v>
+        <v>7.819088280037366</v>
       </c>
       <c r="E26" t="n">
-        <v>18.70842289727105</v>
+        <v>3.040118720806546</v>
       </c>
       <c r="F26" t="n">
-        <v>16.4946284893427</v>
+        <v>2.680377129518189</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
@@ -1280,16 +1280,16 @@
         <v>26</v>
       </c>
       <c r="C27" t="n">
-        <v>34.17098029207339</v>
+        <v>5.552784297461927</v>
       </c>
       <c r="D27" t="n">
-        <v>51.27354478027229</v>
+        <v>8.331951026794247</v>
       </c>
       <c r="E27" t="n">
-        <v>18.70842289727105</v>
+        <v>3.040118720806546</v>
       </c>
       <c r="F27" t="n">
-        <v>16.4946284893427</v>
+        <v>2.680377129518189</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
